--- a/sum.var_AMR_ville_C3G_R.xlsx
+++ b/sum.var_AMR_ville_C3G_R.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="50">
   <si>
     <t xml:space="preserve"/>
   </si>
@@ -23,9 +23,6 @@
     <t xml:space="preserve">log_AMC_EHPAD_FQ</t>
   </si>
   <si>
-    <t xml:space="preserve">log_AMC_EHPAD_aminoglycosides</t>
-  </si>
-  <si>
     <t xml:space="preserve">log_AMC_EHPAD_macrolides</t>
   </si>
   <si>
@@ -56,6 +53,51 @@
     <t xml:space="preserve">log_AMC_ville_tot_except_FQ</t>
   </si>
   <si>
+    <t xml:space="preserve">AMR_ville_C3G_R.1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AMR_animaux_compagnie_amoxi_clav_R</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AMR_animaux_production_C3G_R</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AMR_animaux_production_FQ_R</t>
+  </si>
+  <si>
+    <t xml:space="preserve">veto_by_CV</t>
+  </si>
+  <si>
+    <t xml:space="preserve">log_UGB_density_livestock_tot</t>
+  </si>
+  <si>
+    <t xml:space="preserve">log_UGB_density_porcs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">log_UGB_density_volailles</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AMR_ville_C3G_R.2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">air_NO2_pop</t>
+  </si>
+  <si>
+    <t xml:space="preserve">air_O3_pop</t>
+  </si>
+  <si>
+    <t xml:space="preserve">air_PM10_pop</t>
+  </si>
+  <si>
+    <t xml:space="preserve">air_PM25_pop</t>
+  </si>
+  <si>
+    <t xml:space="preserve">dju_refroi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AMR_ville_C3G_R.3</t>
+  </si>
+  <si>
     <t xml:space="preserve">bac_ou_plus_20_64</t>
   </si>
   <si>
@@ -71,9 +113,6 @@
     <t xml:space="preserve">unemployement_pourc</t>
   </si>
   <si>
-    <t xml:space="preserve">veto_by_CV</t>
-  </si>
-  <si>
     <t xml:space="preserve">APL_medG</t>
   </si>
   <si>
@@ -86,28 +125,7 @@
     <t xml:space="preserve">couv_creche</t>
   </si>
   <si>
-    <t xml:space="preserve">air_NO2_pop</t>
-  </si>
-  <si>
-    <t xml:space="preserve">air_O3_pop</t>
-  </si>
-  <si>
-    <t xml:space="preserve">air_PM10_pop</t>
-  </si>
-  <si>
-    <t xml:space="preserve">air_PM25_pop</t>
-  </si>
-  <si>
-    <t xml:space="preserve">dju_refroi</t>
-  </si>
-  <si>
-    <t xml:space="preserve">log_UGB_density_livestock_tot</t>
-  </si>
-  <si>
-    <t xml:space="preserve">log_UGB_density_porcs</t>
-  </si>
-  <si>
-    <t xml:space="preserve">log_UGB_density_volailles</t>
+    <t xml:space="preserve">pop_3_moins_prop</t>
   </si>
   <si>
     <t xml:space="preserve">Auvergne-Rhone-Alpes</t>
@@ -569,1181 +587,1415 @@
       <c r="AF1" t="s">
         <v>31</v>
       </c>
+      <c r="AG1" t="s">
+        <v>32</v>
+      </c>
+      <c r="AH1" t="s">
+        <v>33</v>
+      </c>
+      <c r="AI1" t="s">
+        <v>34</v>
+      </c>
+      <c r="AJ1" t="s">
+        <v>35</v>
+      </c>
+      <c r="AK1" t="s">
+        <v>36</v>
+      </c>
+      <c r="AL1" t="s">
+        <v>37</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="B2" t="n">
-        <v>-0.00610547820205154</v>
+        <v>-0.00210946111907667</v>
       </c>
       <c r="C2" t="n">
-        <v>0.0227989866658787</v>
+        <v>0.00673395387442586</v>
       </c>
       <c r="D2" t="n">
-        <v>-0.00391553252127912</v>
+        <v>-0.0236791454821986</v>
       </c>
       <c r="E2" t="n">
-        <v>-0.0760709390872229</v>
+        <v>-0.0757500947291418</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.00713689493866628</v>
+        <v>0.10036063159044</v>
       </c>
       <c r="G2" t="n">
-        <v>0.12117932925202</v>
+        <v>0.0335610808107989</v>
       </c>
       <c r="H2" t="n">
-        <v>-0.0808807125717539</v>
+        <v>0.045746548313324</v>
       </c>
       <c r="I2" t="n">
-        <v>0.0813375519024485</v>
+        <v>-0.119218369487267</v>
       </c>
       <c r="J2" t="n">
-        <v>-0.166150175030627</v>
+        <v>-0.0729740524328948</v>
       </c>
       <c r="K2" t="n">
-        <v>-0.0753099080728623</v>
+        <v>-0.11340677064681</v>
       </c>
       <c r="L2" t="n">
-        <v>-0.122122632657002</v>
+        <v>0.037870926705233</v>
       </c>
       <c r="M2" t="n">
-        <v>0.0773511194656334</v>
+        <v>-0.114851315499916</v>
       </c>
       <c r="N2" t="n">
-        <v>-0.122857714317659</v>
+        <v>-0.00210946111907667</v>
       </c>
       <c r="O2" t="n">
-        <v>0.0277501347598573</v>
+        <v>0.0615986685381392</v>
       </c>
       <c r="P2" t="n">
-        <v>0.0516394578746546</v>
+        <v>-0.0057397080210425</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.013549101832271</v>
+        <v>-0.0117322731793835</v>
       </c>
       <c r="R2" t="n">
-        <v>-0.0101010669921438</v>
+        <v>0.0582695830019245</v>
       </c>
       <c r="S2" t="n">
-        <v>0.00348290956367907</v>
+        <v>0.152621661124171</v>
       </c>
       <c r="T2" t="n">
-        <v>0.259298879221153</v>
+        <v>-0.346688833462624</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.132075270155748</v>
+        <v>-0.209548982113039</v>
       </c>
       <c r="V2" t="n">
-        <v>0.149346773238414</v>
+        <v>-0.00210946111907667</v>
       </c>
       <c r="W2" t="n">
-        <v>0.00110532710875983</v>
+        <v>2.46131616730103</v>
       </c>
       <c r="X2" t="n">
-        <v>0.0152766041698991</v>
+        <v>-2.19227167052624</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.49498460134298</v>
+        <v>-0.14689466098425</v>
       </c>
       <c r="Z2" t="n">
-        <v>-3.1629388150638</v>
+        <v>0.464358721866095</v>
       </c>
       <c r="AA2" t="n">
-        <v>-0.188862103365707</v>
+        <v>11.0218902694913</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.657771400481362</v>
+        <v>-0.00210946111907667</v>
       </c>
       <c r="AC2" t="n">
-        <v>3.04099299782066</v>
+        <v>0.0231009862779099</v>
       </c>
       <c r="AD2" t="n">
-        <v>0.163898027736588</v>
+        <v>0.0711842396775379</v>
       </c>
       <c r="AE2" t="n">
-        <v>-0.323990507627599</v>
+        <v>0.0133997267485429</v>
       </c>
       <c r="AF2" t="n">
-        <v>-0.201469048623079</v>
+        <v>-0.0134887005011725</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>-0.0116735390973381</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>-0.23814057256977</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>0.102157056829545</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>-0.0148335863570865</v>
+      </c>
+      <c r="AK2" t="n">
+        <v>0.010521087269544</v>
+      </c>
+      <c r="AL2" t="n">
+        <v>0.00172099403356767</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="B3" t="n">
-        <v>-0.00727792207759585</v>
+        <v>-0.00474447393759493</v>
       </c>
       <c r="C3" t="n">
-        <v>-0.0467451233262862</v>
+        <v>-0.0626853491315937</v>
       </c>
       <c r="D3" t="n">
-        <v>0.0238735065065728</v>
+        <v>0.0667609974418947</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.0206987396103455</v>
+        <v>0.00896430553400415</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.0049694833497094</v>
+        <v>0.0352159793973484</v>
       </c>
       <c r="G3" t="n">
-        <v>0.111029354540155</v>
+        <v>-0.0975259174762126</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.0266083859129174</v>
+        <v>0.0890607105496024</v>
       </c>
       <c r="I3" t="n">
-        <v>0.135613926142571</v>
+        <v>0.0302138660849762</v>
       </c>
       <c r="J3" t="n">
-        <v>-0.00256164215613753</v>
+        <v>0.0138953877725435</v>
       </c>
       <c r="K3" t="n">
-        <v>0.0103011226207277</v>
+        <v>0.0155037622756563</v>
       </c>
       <c r="L3" t="n">
-        <v>-0.0011313276221727</v>
+        <v>0.0966353497022475</v>
       </c>
       <c r="M3" t="n">
-        <v>0.137200939250167</v>
+        <v>0.0175382891813646</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.00198693942446345</v>
+        <v>-0.00474447393759493</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.00856093222052971</v>
+        <v>0.0176599543658448</v>
       </c>
       <c r="P3" t="n">
-        <v>-0.121769049849203</v>
+        <v>-0.00594697343484887</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.0395477376111578</v>
+        <v>0.00718843060368204</v>
       </c>
       <c r="R3" t="n">
-        <v>-0.00955202697407379</v>
+        <v>-0.770302815554919</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.00516809254950174</v>
+        <v>0.117825175411432</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.949487629574545</v>
+        <v>-0.603686124644861</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.0793069585208478</v>
+        <v>-0.671327616035061</v>
       </c>
       <c r="V3" t="n">
-        <v>-0.421974144262473</v>
+        <v>-0.00474447393759493</v>
       </c>
       <c r="W3" t="n">
-        <v>0.0185866566095741</v>
+        <v>-1.78849019467855</v>
       </c>
       <c r="X3" t="n">
-        <v>-0.0150643309190375</v>
+        <v>0.594774917323201</v>
       </c>
       <c r="Y3" t="n">
-        <v>-1.3695336311812</v>
+        <v>-1.71738724827605</v>
       </c>
       <c r="Z3" t="n">
-        <v>-0.251602225656889</v>
+        <v>-0.472378788154204</v>
       </c>
       <c r="AA3" t="n">
-        <v>-1.68261929819898</v>
+        <v>-5.42457052529447</v>
       </c>
       <c r="AB3" t="n">
-        <v>-1.08398984254274</v>
+        <v>-0.00474447393759493</v>
       </c>
       <c r="AC3" t="n">
-        <v>-55.8608537531482</v>
+        <v>-0.00596079190927153</v>
       </c>
       <c r="AD3" t="n">
-        <v>0.130792538951928</v>
+        <v>-0.124494038406793</v>
       </c>
       <c r="AE3" t="n">
-        <v>-0.586249031595373</v>
+        <v>0.0396977072599543</v>
       </c>
       <c r="AF3" t="n">
-        <v>-0.656730869945827</v>
+        <v>-0.0114595398085665</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>-0.00299484608859408</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>-0.0900985847101783</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>-0.430405702605618</v>
+      </c>
+      <c r="AJ3" t="n">
+        <v>0.00420126331280438</v>
+      </c>
+      <c r="AK3" t="n">
+        <v>-0.0209620918427937</v>
+      </c>
+      <c r="AL3" t="n">
+        <v>-0.00212758389752027</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="B4" t="n">
-        <v>-0.00374518512832168</v>
+        <v>-0.00264594119661063</v>
       </c>
       <c r="C4" t="n">
-        <v>-0.140746470953964</v>
+        <v>-0.0839658046014768</v>
       </c>
       <c r="D4" t="n">
-        <v>0.00257581038825052</v>
+        <v>-0.160573643927154</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.183617970931607</v>
+        <v>0.0116350506174326</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.00624257076815509</v>
+        <v>-0.278648268623139</v>
       </c>
       <c r="G4" t="n">
-        <v>-0.343476301081051</v>
+        <v>-0.37338220636912</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.648958375030392</v>
+        <v>-0.204154783015747</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.239566660996442</v>
+        <v>-0.141210710616172</v>
       </c>
       <c r="J4" t="n">
-        <v>-0.203943722301149</v>
+        <v>-0.0223308923262131</v>
       </c>
       <c r="K4" t="n">
-        <v>-0.0198286805785976</v>
+        <v>-0.0794524172790022</v>
       </c>
       <c r="L4" t="n">
-        <v>-0.118308536640616</v>
+        <v>-0.193174881389105</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.228852527624302</v>
+        <v>-0.0732747438842462</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.113510835517452</v>
+        <v>-0.00264594119661063</v>
       </c>
       <c r="O4" t="n">
-        <v>0.0310008113112279</v>
+        <v>-0.0697061783083387</v>
       </c>
       <c r="P4" t="n">
-        <v>-0.0434355780501073</v>
+        <v>-0.00184761400226204</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.0188477005491508</v>
+        <v>-0.0100046443402444</v>
       </c>
       <c r="R4" t="n">
-        <v>-0.0316922734703539</v>
+        <v>-0.0055179876751338</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.0101021650853327</v>
+        <v>1.69130769280195</v>
       </c>
       <c r="T4" t="n">
-        <v>0.00764017624437827</v>
+        <v>2.74556373901538</v>
       </c>
       <c r="U4" t="n">
-        <v>0.415098497866289</v>
+        <v>2.08339580005781</v>
       </c>
       <c r="V4" t="n">
-        <v>0.361199868945771</v>
+        <v>-0.00264594119661063</v>
       </c>
       <c r="W4" t="n">
-        <v>0.00399960808516471</v>
+        <v>-4.31875399729239</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.0533366474791847</v>
+        <v>3.56540005694909</v>
       </c>
       <c r="Y4" t="n">
-        <v>-3.09848283142649</v>
+        <v>-0.782589675263861</v>
       </c>
       <c r="Z4" t="n">
-        <v>4.70192221616382</v>
+        <v>-1.41801144666476</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.277708554007333</v>
+        <v>-42.063917768553</v>
       </c>
       <c r="AB4" t="n">
-        <v>-0.707608792389346</v>
+        <v>-0.00264594119661063</v>
       </c>
       <c r="AC4" t="n">
-        <v>-31.4648541764182</v>
+        <v>0.0545735720995601</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.66839843133639</v>
+        <v>-0.0654341902052057</v>
       </c>
       <c r="AE4" t="n">
-        <v>2.70485895397878</v>
+        <v>0.0180099487089462</v>
       </c>
       <c r="AF4" t="n">
-        <v>2.04909981524149</v>
+        <v>-0.0322092704598475</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>-0.017640294352863</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>0.271938752196663</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>0.0988875903309765</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>-0.000651213151715339</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>-0.041946136308274</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>-0.00197807540185887</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="B5" t="n">
-        <v>-0.00437749364939522</v>
+        <v>-0.0054106891510477</v>
       </c>
       <c r="C5" t="n">
-        <v>-0.106863944176263</v>
+        <v>-0.0980898804713043</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.0072604205026598</v>
+        <v>-0.0460995270754599</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.0833846795753841</v>
+        <v>-0.0856219006310501</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.108325923110666</v>
+        <v>-0.046366232871423</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.0525230084274329</v>
+        <v>-0.130678648965293</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.103793338622981</v>
+        <v>-0.048917726788189</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.0737045122649883</v>
+        <v>-0.0692464942458135</v>
       </c>
       <c r="J5" t="n">
-        <v>-0.0681564288574071</v>
+        <v>-0.0278724541611876</v>
       </c>
       <c r="K5" t="n">
-        <v>-0.0558567786530947</v>
+        <v>-0.0651659970916472</v>
       </c>
       <c r="L5" t="n">
-        <v>-0.0681493626463667</v>
+        <v>-0.0493827395147707</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.0750341125545912</v>
+        <v>-0.0662767394077226</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.0719304102850721</v>
+        <v>-0.0054106891510477</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.00475893330338604</v>
+        <v>-0.0737977140278657</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.128476606361307</v>
+        <v>0.0108436371775343</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.0246518889904745</v>
+        <v>0.0064511956297064</v>
       </c>
       <c r="R5" t="n">
-        <v>-0.00944953472479525</v>
+        <v>-0.602380310114915</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.00953091776207989</v>
+        <v>-0.517661915067306</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.916809250734647</v>
+        <v>-0.268031660005875</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.588779331562012</v>
+        <v>-0.311494422645666</v>
       </c>
       <c r="V5" t="n">
-        <v>-0.965860492276028</v>
+        <v>-0.0054106891510477</v>
       </c>
       <c r="W5" t="n">
-        <v>-0.0615170615513462</v>
+        <v>-3.27804295023073</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.0431754152079666</v>
+        <v>0.103643179064499</v>
       </c>
       <c r="Y5" t="n">
-        <v>-2.50159326171497</v>
+        <v>-1.31587084830012</v>
       </c>
       <c r="Z5" t="n">
-        <v>-1.06292799774263</v>
+        <v>-0.38010878600959</v>
       </c>
       <c r="AA5" t="n">
-        <v>-1.57155066518468</v>
+        <v>-6.61747476724499</v>
       </c>
       <c r="AB5" t="n">
-        <v>-0.20146051900081</v>
+        <v>-0.0054106891510477</v>
       </c>
       <c r="AC5" t="n">
-        <v>-52.2257037571435</v>
+        <v>-0.0139735040891263</v>
       </c>
       <c r="AD5" t="n">
-        <v>-0.489338794285964</v>
+        <v>-0.0889789398903094</v>
       </c>
       <c r="AE5" t="n">
-        <v>-0.280630149920175</v>
+        <v>0.0267904630273537</v>
       </c>
       <c r="AF5" t="n">
-        <v>-0.195025553176616</v>
+        <v>-0.011307532303508</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>0.000275088542728966</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>-0.498774154428945</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>-0.805735820374807</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>-0.00761274426643998</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>-0.0302881325843596</v>
+      </c>
+      <c r="AL5" t="n">
+        <v>-0.000485969982432017</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="B6" t="n">
-        <v>0.00258318448047509</v>
+        <v>-0.000284292065927914</v>
       </c>
       <c r="C6" t="n">
-        <v>0.0866387638384615</v>
+        <v>0.0594823394641421</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.015526190251218</v>
+        <v>0.00138620103745199</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.103825701929883</v>
+        <v>-0.0410338671533221</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.0308543324964791</v>
+        <v>0.183072132285433</v>
       </c>
       <c r="G6" t="n">
-        <v>0.149795514321296</v>
+        <v>-0.0140515295826258</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.200758928243766</v>
+        <v>0.085549861147115</v>
       </c>
       <c r="I6" t="n">
-        <v>0.0653240924236424</v>
+        <v>0.0594315464166114</v>
       </c>
       <c r="J6" t="n">
-        <v>0.0203662392806378</v>
+        <v>0.0972308094678789</v>
       </c>
       <c r="K6" t="n">
-        <v>0.0202523188310269</v>
+        <v>0.0291116808889536</v>
       </c>
       <c r="L6" t="n">
-        <v>0.00962550713235052</v>
+        <v>0.070693667754269</v>
       </c>
       <c r="M6" t="n">
-        <v>0.0568559919777563</v>
+        <v>0.0248295369766438</v>
       </c>
       <c r="N6" t="n">
-        <v>0.00579318208056581</v>
+        <v>-0.000284292065927914</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.0245108491443084</v>
+        <v>0.0389302205968238</v>
       </c>
       <c r="P6" t="n">
-        <v>-0.0969276646772585</v>
+        <v>0.0145774880585199</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.0176522562807752</v>
+        <v>-0.000123590283420022</v>
       </c>
       <c r="R6" t="n">
-        <v>0.00565249275238633</v>
+        <v>-0.423678741868557</v>
       </c>
       <c r="S6" t="n">
-        <v>0.00216696854004953</v>
+        <v>-0.122399969203203</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.819762691244818</v>
+        <v>-0.388364951192247</v>
       </c>
       <c r="U6" t="n">
-        <v>0.155428919578729</v>
+        <v>-0.595670602562299</v>
       </c>
       <c r="V6" t="n">
-        <v>-0.219544013778863</v>
+        <v>-0.000284292065927914</v>
       </c>
       <c r="W6" t="n">
-        <v>0.00814653507744779</v>
+        <v>0.647163158559724</v>
       </c>
       <c r="X6" t="n">
-        <v>0.0348548143041566</v>
+        <v>-3.1904011933925</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.0549245784640871</v>
+        <v>-0.453595963951475</v>
       </c>
       <c r="Z6" t="n">
-        <v>-2.28307705009712</v>
+        <v>0.622946781722748</v>
       </c>
       <c r="AA6" t="n">
-        <v>-1.00049179053382</v>
+        <v>-15.8994468340273</v>
       </c>
       <c r="AB6" t="n">
-        <v>-0.751013983466864</v>
+        <v>-0.000284292065927914</v>
       </c>
       <c r="AC6" t="n">
-        <v>-72.5190584647254</v>
+        <v>-0.014554793648164</v>
       </c>
       <c r="AD6" t="n">
-        <v>-0.110874928781878</v>
+        <v>-0.0879917342022967</v>
       </c>
       <c r="AE6" t="n">
-        <v>-0.37363890200651</v>
+        <v>0.0198687079575747</v>
       </c>
       <c r="AF6" t="n">
-        <v>-0.477447968355574</v>
+        <v>0.00373493005830028</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>0.00822729452788746</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>0.0877323322809686</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>-0.190653634970529</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>0.01883440585126</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>0.0118321019448495</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>-0.000799265942887367</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="B7" t="n">
-        <v>-0.00330983799688827</v>
+        <v>-0.00236412055510282</v>
       </c>
       <c r="C7" t="n">
-        <v>0.173274163425219</v>
+        <v>0.0614207298724778</v>
       </c>
       <c r="D7" t="n">
-        <v>0.00142396658869154</v>
+        <v>-0.0145088813068838</v>
       </c>
       <c r="E7" t="n">
-        <v>0.0285967329455456</v>
+        <v>0.110606121684165</v>
       </c>
       <c r="F7" t="n">
-        <v>0.141630383776783</v>
+        <v>0.0601744798308835</v>
       </c>
       <c r="G7" t="n">
-        <v>0.0536157157528258</v>
+        <v>-0.188331569638821</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.0261523399039344</v>
+        <v>0.0406597387657337</v>
       </c>
       <c r="I7" t="n">
-        <v>0.0809305374955791</v>
+        <v>0.0874935060532407</v>
       </c>
       <c r="J7" t="n">
-        <v>0.0829862113056558</v>
+        <v>0.0239107660601627</v>
       </c>
       <c r="K7" t="n">
-        <v>0.0533242943046529</v>
+        <v>0.105554071475889</v>
       </c>
       <c r="L7" t="n">
-        <v>0.123952887678216</v>
+        <v>0.0383246834572868</v>
       </c>
       <c r="M7" t="n">
-        <v>0.0839764245254541</v>
+        <v>0.111511245163811</v>
       </c>
       <c r="N7" t="n">
-        <v>0.129365364213217</v>
+        <v>-0.00236412055510282</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.0379731515184119</v>
+        <v>-0.0184311770127115</v>
       </c>
       <c r="P7" t="n">
-        <v>-0.130848673943125</v>
+        <v>-0.000652098137484839</v>
       </c>
       <c r="Q7" t="n">
-        <v>-0.0107484999537953</v>
+        <v>-0.0064557992462484</v>
       </c>
       <c r="R7" t="n">
-        <v>0.0316780720437211</v>
+        <v>0.138826687668009</v>
       </c>
       <c r="S7" t="n">
-        <v>0.0156868942463988</v>
+        <v>0.289059744010996</v>
       </c>
       <c r="T7" t="n">
-        <v>0.179848586018995</v>
+        <v>0.308994584925497</v>
       </c>
       <c r="U7" t="n">
-        <v>0.392105643161906</v>
+        <v>0.197995368697023</v>
       </c>
       <c r="V7" t="n">
-        <v>-0.634437889386094</v>
+        <v>-0.00236412055510282</v>
       </c>
       <c r="W7" t="n">
-        <v>0.000506652082339015</v>
+        <v>1.12134033295021</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.0403763103815386</v>
+        <v>-5.94298722785559</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.10444105982622</v>
+        <v>2.15545868450043</v>
       </c>
       <c r="Z7" t="n">
-        <v>-4.91147936220112</v>
+        <v>1.54602068082667</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.25840219635609</v>
+        <v>-32.1995523411849</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.637872949977439</v>
+        <v>-0.00236412055510282</v>
       </c>
       <c r="AC7" t="n">
-        <v>-65.5738121330756</v>
+        <v>-0.0484867898515297</v>
       </c>
       <c r="AD7" t="n">
-        <v>0.310915271453248</v>
+        <v>-0.130900303696153</v>
       </c>
       <c r="AE7" t="n">
-        <v>0.282779664596387</v>
+        <v>-0.0097474141827183</v>
       </c>
       <c r="AF7" t="n">
-        <v>0.296184066760388</v>
+        <v>0.0367801772712077</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>0.0262124964709996</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>0.357638558366775</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>-0.563513299647262</v>
+      </c>
+      <c r="AJ7" t="n">
+        <v>0.018776500720234</v>
+      </c>
+      <c r="AK7" t="n">
+        <v>-0.0501937303954304</v>
+      </c>
+      <c r="AL7" t="n">
+        <v>0.00341200918641746</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="B8" t="n">
-        <v>0.0239737842463818</v>
+        <v>0.0145441901312369</v>
       </c>
       <c r="C8" t="n">
-        <v>-0.0761982067032024</v>
+        <v>-0.106665696028367</v>
       </c>
       <c r="D8" t="n">
-        <v>0.00101309380513934</v>
+        <v>-0.00210520011203225</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.0443218255085664</v>
+        <v>-0.0041952574902393</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.0474864701729299</v>
+        <v>-0.0883645155060498</v>
       </c>
       <c r="G8" t="n">
-        <v>0.0320282106069829</v>
+        <v>0.309219299525867</v>
       </c>
       <c r="H8" t="n">
-        <v>0.285066640625593</v>
+        <v>0.0567337331081234</v>
       </c>
       <c r="I8" t="n">
-        <v>0.0453591787073651</v>
+        <v>0.0138111941148235</v>
       </c>
       <c r="J8" t="n">
-        <v>0.0561470107958103</v>
+        <v>0.263100653547779</v>
       </c>
       <c r="K8" t="n">
-        <v>0.308860302034807</v>
+        <v>0.0823716821161474</v>
       </c>
       <c r="L8" t="n">
-        <v>0.107748297219291</v>
+        <v>0.0757260764774565</v>
       </c>
       <c r="M8" t="n">
-        <v>0.0456105311536912</v>
+        <v>0.0918117366690664</v>
       </c>
       <c r="N8" t="n">
-        <v>0.117006518966685</v>
+        <v>0.0145441901312369</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.0063807621527126</v>
+        <v>-0.0180170457820621</v>
       </c>
       <c r="P8" t="n">
-        <v>0.573783024870932</v>
+        <v>-0.00203471874096844</v>
       </c>
       <c r="Q8" t="n">
-        <v>-0.101548228441481</v>
+        <v>-0.00704514598014381</v>
       </c>
       <c r="R8" t="n">
-        <v>0.0174471364361519</v>
+        <v>1.71905337412741</v>
       </c>
       <c r="S8" t="n">
-        <v>0.0102000575278649</v>
+        <v>-1.89651190208578</v>
       </c>
       <c r="T8" t="n">
-        <v>2.15055758762769</v>
+        <v>-1.22021097105653</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.522351338233364</v>
+        <v>-0.810419476847576</v>
       </c>
       <c r="V8" t="n">
-        <v>0.65397987258603</v>
+        <v>0.0145441901312369</v>
       </c>
       <c r="W8" t="n">
-        <v>-0.0135354397484868</v>
+        <v>11.0611048510848</v>
       </c>
       <c r="X8" t="n">
-        <v>0.111785208040009</v>
+        <v>-8.13657157043532</v>
       </c>
       <c r="Y8" t="n">
-        <v>8.26736980387867</v>
+        <v>1.89965622981696</v>
       </c>
       <c r="Z8" t="n">
-        <v>-5.52486089049018</v>
+        <v>1.2231669853248</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.42896583509715</v>
+        <v>-14.3772288344109</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.22097937624756</v>
+        <v>0.0145441901312369</v>
       </c>
       <c r="AC8" t="n">
-        <v>-59.7466680389308</v>
+        <v>0.00718328310658834</v>
       </c>
       <c r="AD8" t="n">
-        <v>-1.86482060595842</v>
+        <v>0.623368914024887</v>
       </c>
       <c r="AE8" t="n">
-        <v>-1.20431620584416</v>
+        <v>-0.104572526869896</v>
       </c>
       <c r="AF8" t="n">
-        <v>-0.709160811419627</v>
+        <v>0.0145650987656854</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>-0.00235061950876203</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>-0.364227869492569</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>0.868083983240932</v>
+      </c>
+      <c r="AJ8" t="n">
+        <v>-0.0457772676852642</v>
+      </c>
+      <c r="AK8" t="n">
+        <v>0.103648576807794</v>
+      </c>
+      <c r="AL8" t="n">
+        <v>0.00697314120095147</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="B9" t="n">
-        <v>-0.0073706056933802</v>
+        <v>-0.005367603900993</v>
       </c>
       <c r="C9" t="n">
-        <v>0.066864101862825</v>
+        <v>0.0346589884140389</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.0200093589283057</v>
+        <v>0.111605333198221</v>
       </c>
       <c r="E9" t="n">
-        <v>0.0994395899840363</v>
+        <v>0.0962525363404283</v>
       </c>
       <c r="F9" t="n">
-        <v>0.131407276379609</v>
+        <v>0.0504734259398501</v>
       </c>
       <c r="G9" t="n">
-        <v>0.0127262086767501</v>
+        <v>-0.208271122741779</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.0553671062272829</v>
+        <v>0.0986245611203094</v>
       </c>
       <c r="I9" t="n">
-        <v>0.178641490445863</v>
+        <v>0.0786633420934962</v>
       </c>
       <c r="J9" t="n">
-        <v>0.0417892534060859</v>
+        <v>-0.0324191136737228</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.019218511581013</v>
+        <v>0.0383287535447493</v>
       </c>
       <c r="L9" t="n">
-        <v>0.0470995087582011</v>
+        <v>0.104722423510447</v>
       </c>
       <c r="M9" t="n">
-        <v>0.195704363637368</v>
+        <v>0.0416848994848347</v>
       </c>
       <c r="N9" t="n">
-        <v>0.0486946919350665</v>
+        <v>-0.005367603900993</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.00947564638642428</v>
+        <v>0.0153132104459661</v>
       </c>
       <c r="P9" t="n">
-        <v>-0.0851388989416012</v>
+        <v>-0.000969293831558328</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.0328469659685514</v>
+        <v>-0.00545927080555194</v>
       </c>
       <c r="R9" t="n">
-        <v>-0.00854581958948238</v>
+        <v>-0.314908419026853</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.00151144721836832</v>
+        <v>0.785942009562261</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.435925064440227</v>
+        <v>0.487882730365099</v>
       </c>
       <c r="U9" t="n">
-        <v>0.0470364211183201</v>
+        <v>-0.0374455911788562</v>
       </c>
       <c r="V9" t="n">
-        <v>-0.601602770183393</v>
+        <v>-0.005367603900993</v>
       </c>
       <c r="W9" t="n">
-        <v>0.00185087729647237</v>
+        <v>-1.67028852900829</v>
       </c>
       <c r="X9" t="n">
-        <v>-0.0532911174132354</v>
+        <v>-0.0109312412913779</v>
       </c>
       <c r="Y9" t="n">
-        <v>-0.768125665259879</v>
+        <v>-0.191921675231057</v>
       </c>
       <c r="Z9" t="n">
-        <v>0.186917479833839</v>
+        <v>-0.336248048840461</v>
       </c>
       <c r="AA9" t="n">
-        <v>-0.513389147401974</v>
+        <v>-38.3424138223202</v>
       </c>
       <c r="AB9" t="n">
-        <v>0.151057613194073</v>
+        <v>-0.005367603900993</v>
       </c>
       <c r="AC9" t="n">
-        <v>-56.4837095748711</v>
+        <v>-0.0309050695110712</v>
       </c>
       <c r="AD9" t="n">
-        <v>0.783655282699356</v>
+        <v>-0.085804112752481</v>
       </c>
       <c r="AE9" t="n">
-        <v>0.473431711990435</v>
+        <v>0.0321586612015137</v>
       </c>
       <c r="AF9" t="n">
-        <v>-0.0300025543366282</v>
+        <v>-0.00673117719952007</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>0.00173258813346108</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>-0.0206447053958451</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>-0.56047013214129</v>
+      </c>
+      <c r="AJ9" t="n">
+        <v>-0.000343998372898837</v>
+      </c>
+      <c r="AK9" t="n">
+        <v>-0.0496410442958685</v>
+      </c>
+      <c r="AL9" t="n">
+        <v>-0.000229650166180577</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="B10" t="n">
-        <v>-0.00428444464804462</v>
+        <v>-0.00264098554893809</v>
       </c>
       <c r="C10" t="n">
-        <v>0.0580484019414118</v>
+        <v>0.0975994435577037</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.00439116732998016</v>
+        <v>0.0233719976102421</v>
       </c>
       <c r="E10" t="n">
-        <v>0.00942039501627749</v>
+        <v>0.0395856823912233</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.00833308192360844</v>
+        <v>0.0849547857042242</v>
       </c>
       <c r="G10" t="n">
-        <v>0.0590881138113237</v>
+        <v>0.0601430323680632</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.0770381671136652</v>
+        <v>0.0292138845299469</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.023095940086888</v>
+        <v>0.00620438066090511</v>
       </c>
       <c r="J10" t="n">
-        <v>0.0138250468774766</v>
+        <v>-0.0506951096157239</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.0465870670717229</v>
+        <v>0.0325507305764863</v>
       </c>
       <c r="L10" t="n">
-        <v>0.0281726209203691</v>
+        <v>0.0218218940632773</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.0321188808271105</v>
+        <v>0.0274333514639498</v>
       </c>
       <c r="N10" t="n">
-        <v>0.0258050253660344</v>
+        <v>-0.00264098554893809</v>
       </c>
       <c r="O10" t="n">
-        <v>0.020029425100556</v>
+        <v>0.0800068228600296</v>
       </c>
       <c r="P10" t="n">
-        <v>-0.0742761836449131</v>
+        <v>-0.00540575234929896</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.0049517994584258</v>
+        <v>-0.00579879783185996</v>
       </c>
       <c r="R10" t="n">
-        <v>-0.00754585057428884</v>
+        <v>-0.317730159419209</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.000273540182244905</v>
+        <v>0.120572232824682</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.41243639403738</v>
+        <v>-0.117960350491315</v>
       </c>
       <c r="U10" t="n">
-        <v>0.213089531958767</v>
+        <v>0.322043412432475</v>
       </c>
       <c r="V10" t="n">
-        <v>0.393624918490865</v>
+        <v>-0.00264098554893809</v>
       </c>
       <c r="W10" t="n">
-        <v>-0.00695265113598446</v>
+        <v>-3.36054905774655</v>
       </c>
       <c r="X10" t="n">
-        <v>-0.0187614298914516</v>
+        <v>0.125640023711585</v>
       </c>
       <c r="Y10" t="n">
-        <v>-2.82939098760496</v>
+        <v>-1.05862112080309</v>
       </c>
       <c r="Z10" t="n">
-        <v>-0.781407843276192</v>
+        <v>-0.969569942067806</v>
       </c>
       <c r="AA10" t="n">
-        <v>-0.158930441113735</v>
+        <v>20.4716391934634</v>
       </c>
       <c r="AB10" t="n">
-        <v>-0.407920590719671</v>
+        <v>-0.00264098554893809</v>
       </c>
       <c r="AC10" t="n">
-        <v>76.4027241779897</v>
+        <v>0.0165868695718829</v>
       </c>
       <c r="AD10" t="n">
-        <v>0.0450234909322833</v>
+        <v>-0.0682606175468987</v>
       </c>
       <c r="AE10" t="n">
-        <v>-0.0781902418861564</v>
+        <v>0.00640762906621618</v>
       </c>
       <c r="AF10" t="n">
-        <v>0.0563851631786323</v>
+        <v>-0.00569589876732141</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>-0.00231622520835979</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>0.226721715917034</v>
+      </c>
+      <c r="AI10" t="n">
+        <v>0.255688366175892</v>
+      </c>
+      <c r="AJ10" t="n">
+        <v>0.00678206785536286</v>
+      </c>
+      <c r="AK10" t="n">
+        <v>0.000487602492993006</v>
+      </c>
+      <c r="AL10" t="n">
+        <v>-0.00423125097371813</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="B11" t="n">
-        <v>0.00194258131006261</v>
+        <v>0.00157711312072683</v>
       </c>
       <c r="C11" t="n">
-        <v>0.0160059031384701</v>
+        <v>0.0860160295965499</v>
       </c>
       <c r="D11" t="n">
-        <v>0.00846553313490665</v>
+        <v>0.02995211991031</v>
       </c>
       <c r="E11" t="n">
-        <v>0.0715283036037904</v>
+        <v>0.00953556340121431</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.0206132949650322</v>
+        <v>0.0158617624856274</v>
       </c>
       <c r="G11" t="n">
-        <v>-0.0774082714138076</v>
+        <v>0.313060253546427</v>
       </c>
       <c r="H11" t="n">
-        <v>0.557782375930676</v>
+        <v>-0.0427652547046527</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.0153157191070746</v>
+        <v>0.042769586516405</v>
       </c>
       <c r="J11" t="n">
-        <v>0.0661033386147282</v>
+        <v>-0.0434899261813493</v>
       </c>
       <c r="K11" t="n">
-        <v>-0.0489044650010751</v>
+        <v>0.03321280075391</v>
       </c>
       <c r="L11" t="n">
-        <v>0.0209677708944</v>
+        <v>-0.0505408090917457</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.00664344797551496</v>
+        <v>0.0233233898465209</v>
       </c>
       <c r="N11" t="n">
-        <v>0.0142927395876646</v>
+        <v>0.00157711312072683</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.000591356126422435</v>
+        <v>-0.0140129434087858</v>
       </c>
       <c r="P11" t="n">
-        <v>-0.108889977288115</v>
+        <v>0.0169332582755317</v>
       </c>
       <c r="Q11" t="n">
-        <v>-0.0256443485744775</v>
+        <v>0.0533113040488226</v>
       </c>
       <c r="R11" t="n">
-        <v>0.0298461140178588</v>
+        <v>0.128949509529747</v>
       </c>
       <c r="S11" t="n">
-        <v>0.0104522679279904</v>
+        <v>-0.268724626977033</v>
       </c>
       <c r="T11" t="n">
-        <v>0.500460406153616</v>
+        <v>-0.489446482450284</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.0512081488565186</v>
+        <v>-0.48313178901756</v>
       </c>
       <c r="V11" t="n">
-        <v>0.438639498601624</v>
+        <v>0.00157711312072683</v>
       </c>
       <c r="W11" t="n">
-        <v>0.0344118500363214</v>
+        <v>-1.42640909208072</v>
       </c>
       <c r="X11" t="n">
-        <v>0.0271367628666701</v>
+        <v>5.91211095973774</v>
       </c>
       <c r="Y11" t="n">
-        <v>-1.27025301167474</v>
+        <v>-0.895613718645758</v>
       </c>
       <c r="Z11" t="n">
-        <v>3.77731543818017</v>
+        <v>-0.823422918814776</v>
       </c>
       <c r="AA11" t="n">
-        <v>0.453108639272595</v>
+        <v>64.7608500031866</v>
       </c>
       <c r="AB11" t="n">
-        <v>0.0694029333978714</v>
+        <v>0.00157711312072683</v>
       </c>
       <c r="AC11" t="n">
-        <v>166.62976501752</v>
+        <v>0.00457331816569248</v>
       </c>
       <c r="AD11" t="n">
-        <v>-0.294345454836203</v>
+        <v>-0.0794686588701281</v>
       </c>
       <c r="AE11" t="n">
-        <v>-0.491427873970418</v>
+        <v>-0.022730959003571</v>
       </c>
       <c r="AF11" t="n">
-        <v>-0.586790574622009</v>
+        <v>0.028768876407479</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>0.00562799823828984</v>
+      </c>
+      <c r="AH11" t="n">
+        <v>0.132832947960337</v>
+      </c>
+      <c r="AI11" t="n">
+        <v>0.482211586012499</v>
+      </c>
+      <c r="AJ11" t="n">
+        <v>0.0253117043650773</v>
+      </c>
+      <c r="AK11" t="n">
+        <v>0.0316327784762719</v>
+      </c>
+      <c r="AL11" t="n">
+        <v>-0.00230109366776357</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="B12" t="n">
-        <v>0.0192407351155962</v>
+        <v>0.0180938976227369</v>
       </c>
       <c r="C12" t="n">
-        <v>0.171796636369892</v>
+        <v>0.16928729582152</v>
       </c>
       <c r="D12" t="n">
-        <v>0.0320828793988181</v>
+        <v>0.181161651205074</v>
       </c>
       <c r="E12" t="n">
-        <v>0.554094433397117</v>
+        <v>0.0151993913420284</v>
       </c>
       <c r="F12" t="n">
-        <v>0.0585231889869436</v>
+        <v>0.12082021118173</v>
       </c>
       <c r="G12" t="n">
-        <v>0.14509785139417</v>
+        <v>0.467253145695357</v>
       </c>
       <c r="H12" t="n">
-        <v>0.386616207851143</v>
+        <v>0.0122705756134747</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.0808845123938792</v>
+        <v>0.198025239949699</v>
       </c>
       <c r="J12" t="n">
-        <v>0.43124139464155</v>
+        <v>-0.00197631555638445</v>
       </c>
       <c r="K12" t="n">
-        <v>0.0165723088463988</v>
+        <v>0.094141686407852</v>
       </c>
       <c r="L12" t="n">
-        <v>0.180682108931934</v>
+        <v>-0.00172738073185696</v>
       </c>
       <c r="M12" t="n">
-        <v>-0.105806632153172</v>
+        <v>0.0855989607660336</v>
       </c>
       <c r="N12" t="n">
-        <v>0.177400912505652</v>
+        <v>0.0180938976227369</v>
       </c>
       <c r="O12" t="n">
-        <v>-0.0184094905101016</v>
+        <v>0.025588352033364</v>
       </c>
       <c r="P12" t="n">
-        <v>0.162931327655325</v>
+        <v>-0.0158690518044377</v>
       </c>
       <c r="Q12" t="n">
-        <v>-0.0559528674592195</v>
+        <v>-0.00954756689330399</v>
       </c>
       <c r="R12" t="n">
-        <v>0.0280310139591237</v>
+        <v>1.02430888453424</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.0043031680659485</v>
+        <v>-1.59565512176468</v>
       </c>
       <c r="T12" t="n">
-        <v>1.48859703176717</v>
+        <v>-1.18205595693551</v>
       </c>
       <c r="U12" t="n">
-        <v>0.302695896886023</v>
+        <v>-1.35410658786014</v>
       </c>
       <c r="V12" t="n">
-        <v>1.29365625073829</v>
+        <v>0.0180938976227369</v>
       </c>
       <c r="W12" t="n">
-        <v>0.0354294214924339</v>
+        <v>4.24082559502784</v>
       </c>
       <c r="X12" t="n">
-        <v>0.0638621769674025</v>
+        <v>6.72187461778694</v>
       </c>
       <c r="Y12" t="n">
-        <v>3.77293020223013</v>
+        <v>3.20570944017448</v>
       </c>
       <c r="Z12" t="n">
-        <v>7.80705501253983</v>
+        <v>1.13064796511604</v>
       </c>
       <c r="AA12" t="n">
-        <v>2.10194285291135</v>
+        <v>69.5078139826724</v>
       </c>
       <c r="AB12" t="n">
-        <v>0.515189470637316</v>
+        <v>0.0180938976227369</v>
       </c>
       <c r="AC12" t="n">
-        <v>138.86489018101</v>
+        <v>-0.0156387845446128</v>
       </c>
       <c r="AD12" t="n">
-        <v>-1.53500051822768</v>
+        <v>0.0495522387392417</v>
       </c>
       <c r="AE12" t="n">
-        <v>-1.14982521262975</v>
+        <v>-0.0605144058354366</v>
       </c>
       <c r="AF12" t="n">
-        <v>-1.3485258279328</v>
+        <v>0.0302788951199366</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>0.0059130078110877</v>
+      </c>
+      <c r="AH12" t="n">
+        <v>0.283442369376223</v>
+      </c>
+      <c r="AI12" t="n">
+        <v>1.25678752951199</v>
+      </c>
+      <c r="AJ12" t="n">
+        <v>0.0336430218234816</v>
+      </c>
+      <c r="AK12" t="n">
+        <v>0.0696894773037612</v>
+      </c>
+      <c r="AL12" t="n">
+        <v>-0.00110592499070373</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="B13" t="n">
-        <v>-0.0112693177568383</v>
+        <v>-0.00864763339940884</v>
       </c>
       <c r="C13" t="n">
-        <v>-0.224873212082442</v>
+        <v>-0.163792050368117</v>
       </c>
       <c r="D13" t="n">
-        <v>-0.0183321202889362</v>
+        <v>-0.167271902499466</v>
       </c>
       <c r="E13" t="n">
-        <v>-0.251159598303758</v>
+        <v>-0.0851775313067445</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.0975987974180862</v>
+        <v>-0.237554391414924</v>
       </c>
       <c r="G13" t="n">
-        <v>-0.211152717433232</v>
+        <v>-0.170995817172662</v>
       </c>
       <c r="H13" t="n">
-        <v>-0.00990787078072184</v>
+        <v>-0.162021848639044</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.154639432268191</v>
+        <v>-0.186937087540904</v>
       </c>
       <c r="J13" t="n">
-        <v>-0.271646526576622</v>
+        <v>-0.146379752900888</v>
       </c>
       <c r="K13" t="n">
-        <v>-0.143604935679247</v>
+        <v>-0.172749983022184</v>
       </c>
       <c r="L13" t="n">
-        <v>-0.208536841968602</v>
+        <v>-0.150969210942737</v>
       </c>
       <c r="M13" t="n">
-        <v>-0.14824376887538</v>
+        <v>-0.16932861076034</v>
       </c>
       <c r="N13" t="n">
-        <v>-0.208072535110238</v>
+        <v>-0.00864763339940884</v>
       </c>
       <c r="O13" t="n">
-        <v>0.0318807501906553</v>
+        <v>-0.0451321703004038</v>
       </c>
       <c r="P13" t="n">
-        <v>0.00140882235471387</v>
+        <v>-0.00388917318968417</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.0418464937381661</v>
+        <v>-0.010783841722055</v>
       </c>
       <c r="R13" t="n">
-        <v>-0.0357682568841039</v>
+        <v>-0.63488960520175</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.0110997669425068</v>
+        <v>1.2436250193625</v>
       </c>
       <c r="T13" t="n">
-        <v>-1.05198163700138</v>
+        <v>1.07400427593327</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.151733863241545</v>
+        <v>1.8697104870729</v>
       </c>
       <c r="V13" t="n">
-        <v>-0.447027872714139</v>
+        <v>-0.00864763339940884</v>
       </c>
       <c r="W13" t="n">
-        <v>-0.0220317753526957</v>
+        <v>-3.68921628388639</v>
       </c>
       <c r="X13" t="n">
-        <v>-0.028910315055723</v>
+        <v>2.44971914892797</v>
       </c>
       <c r="Y13" t="n">
-        <v>-2.85727085687985</v>
+        <v>-0.698329443036231</v>
       </c>
       <c r="Z13" t="n">
-        <v>1.50508403781023</v>
+        <v>-0.587401204304756</v>
       </c>
       <c r="AA13" t="n">
-        <v>-0.404284631845628</v>
+        <v>-10.837588555778</v>
       </c>
       <c r="AB13" t="n">
-        <v>-0.100280015816208</v>
+        <v>-0.00864763339940884</v>
       </c>
       <c r="AC13" t="n">
-        <v>8.93628752397186</v>
+        <v>0.0235017043321414</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.19169725898034</v>
+        <v>-0.0127727968714012</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.02719779491453</v>
+        <v>0.0412324619215205</v>
       </c>
       <c r="AF13" t="n">
-        <v>1.80348416323166</v>
+        <v>-0.0332358585826731</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>-0.0110129494685375</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>-0.148420789500691</v>
+      </c>
+      <c r="AI13" t="n">
+        <v>-0.513037522362324</v>
+      </c>
+      <c r="AJ13" t="n">
+        <v>-0.0383301540948154</v>
+      </c>
+      <c r="AK13" t="n">
+        <v>-0.0347804888684874</v>
+      </c>
+      <c r="AL13" t="n">
+        <v>0.00115267060212793</v>
       </c>
     </row>
   </sheetData>
